--- a/data/final/series/comexstat_celulose_nao_coniferas_exp_kg.xlsx
+++ b/data/final/series/comexstat_celulose_nao_coniferas_exp_kg.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1072,6 +1072,14 @@
         <v>1412673002</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1801287673</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
